--- a/mi_base_de_datos.xlsx
+++ b/mi_base_de_datos.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/martinitozzz/Desktop/CICLO 2026-1/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1c3653fb7a39d195/Escritorio/paginaweb/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36D06C52-5EDA-6242-8BC8-380E67EBA282}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{36D06C52-5EDA-6242-8BC8-380E67EBA282}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2989D494-7841-44C1-9F05-1ACA2E7B5848}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17360" xr2:uid="{2FF5BE82-DD0C-854B-AEE7-2308CDD7AC52}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2FF5BE82-DD0C-854B-AEE7-2308CDD7AC52}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -2223,7 +2223,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -2252,6 +2252,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -2270,10 +2278,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2282,8 +2291,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -2617,24 +2628,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0391EA6-0327-B044-BF53-8399DF6C5E5D}">
   <dimension ref="A1:Q147"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="68.6640625" customWidth="1"/>
-    <col min="2" max="2" width="30.6640625" customWidth="1"/>
+    <col min="1" max="1" width="68.625" customWidth="1"/>
+    <col min="2" max="2" width="30.625" customWidth="1"/>
     <col min="3" max="3" width="16.5" customWidth="1"/>
-    <col min="5" max="5" width="15.33203125" customWidth="1"/>
-    <col min="6" max="6" width="26.33203125" customWidth="1"/>
+    <col min="5" max="5" width="15.375" customWidth="1"/>
+    <col min="6" max="6" width="26.375" customWidth="1"/>
     <col min="8" max="8" width="72" customWidth="1"/>
-    <col min="9" max="9" width="82.83203125" customWidth="1"/>
-    <col min="10" max="10" width="13.83203125" customWidth="1"/>
+    <col min="9" max="9" width="82.875" customWidth="1"/>
+    <col min="10" max="10" width="13.875" customWidth="1"/>
     <col min="11" max="11" width="50.5" customWidth="1"/>
-    <col min="12" max="12" width="28.83203125" customWidth="1"/>
-    <col min="15" max="15" width="106.83203125" customWidth="1"/>
+    <col min="12" max="12" width="28.875" customWidth="1"/>
+    <col min="15" max="15" width="106.875" customWidth="1"/>
     <col min="16" max="16" width="109" customWidth="1"/>
     <col min="17" max="17" width="108.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>101</v>
       </c>
@@ -2687,7 +2698,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:17">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -2722,7 +2733,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="3" spans="1:17">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -2757,7 +2768,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="4" spans="1:17">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -2792,7 +2803,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="5" spans="1:17">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -2827,7 +2838,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="6" spans="1:17">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>20</v>
       </c>
@@ -2862,7 +2873,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="7" spans="1:17">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>21</v>
       </c>
@@ -2897,7 +2908,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="8" spans="1:17">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>22</v>
       </c>
@@ -2932,7 +2943,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="9" spans="1:17">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>23</v>
       </c>
@@ -2967,7 +2978,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="10" spans="1:17">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>24</v>
       </c>
@@ -3002,7 +3013,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="11" spans="1:17">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>25</v>
       </c>
@@ -3037,7 +3048,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="12" spans="1:17">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>26</v>
       </c>
@@ -3072,7 +3083,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="13" spans="1:17">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>27</v>
       </c>
@@ -3107,7 +3118,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="14" spans="1:17">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>28</v>
       </c>
@@ -3142,7 +3153,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="15" spans="1:17">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>29</v>
       </c>
@@ -3177,7 +3188,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="16" spans="1:17">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>31</v>
       </c>
@@ -3209,7 +3220,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="17" spans="1:17">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>32</v>
       </c>
@@ -3241,7 +3252,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="18" spans="1:17">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>33</v>
       </c>
@@ -3273,7 +3284,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="19" spans="1:17">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>34</v>
       </c>
@@ -3308,7 +3319,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="20" spans="1:17">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>35</v>
       </c>
@@ -3340,7 +3351,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="21" spans="1:17">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>36</v>
       </c>
@@ -3375,7 +3386,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="22" spans="1:17">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>37</v>
       </c>
@@ -3410,7 +3421,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="23" spans="1:17">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>38</v>
       </c>
@@ -3448,7 +3459,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="24" spans="1:17">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>40</v>
       </c>
@@ -3483,7 +3494,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="25" spans="1:17">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>41</v>
       </c>
@@ -3518,7 +3529,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="26" spans="1:17">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>48</v>
       </c>
@@ -3553,7 +3564,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="27" spans="1:17">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>42</v>
       </c>
@@ -3585,7 +3596,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="28" spans="1:17">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>43</v>
       </c>
@@ -3623,7 +3634,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="29" spans="1:17">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>45</v>
       </c>
@@ -3658,7 +3669,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="30" spans="1:17">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>46</v>
       </c>
@@ -3690,7 +3701,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="31" spans="1:17">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>47</v>
       </c>
@@ -3725,7 +3736,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="32" spans="1:17">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>50</v>
       </c>
@@ -3775,7 +3786,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="33" spans="1:17">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>51</v>
       </c>
@@ -3825,7 +3836,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="34" spans="1:17">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>52</v>
       </c>
@@ -3860,7 +3871,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="35" spans="1:17">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>53</v>
       </c>
@@ -3910,7 +3921,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="36" spans="1:17">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>54</v>
       </c>
@@ -3960,7 +3971,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="37" spans="1:17">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>55</v>
       </c>
@@ -3995,7 +4006,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="38" spans="1:17">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>56</v>
       </c>
@@ -4030,7 +4041,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="39" spans="1:17">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>57</v>
       </c>
@@ -4065,7 +4076,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="40" spans="1:17">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>58</v>
       </c>
@@ -4100,7 +4111,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="41" spans="1:17">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>59</v>
       </c>
@@ -4150,7 +4161,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="42" spans="1:17">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>60</v>
       </c>
@@ -4185,7 +4196,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="43" spans="1:17">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>61</v>
       </c>
@@ -4235,7 +4246,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="44" spans="1:17">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>63</v>
       </c>
@@ -4285,7 +4296,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="45" spans="1:17">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>64</v>
       </c>
@@ -4335,7 +4346,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="46" spans="1:17">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>65</v>
       </c>
@@ -4385,7 +4396,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="47" spans="1:17">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>66</v>
       </c>
@@ -4435,7 +4446,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="48" spans="1:17">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>67</v>
       </c>
@@ -4485,7 +4496,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="49" spans="1:17">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>68</v>
       </c>
@@ -4504,7 +4515,7 @@
       <c r="G49" s="5">
         <v>0.17569444444444443</v>
       </c>
-      <c r="H49" t="s">
+      <c r="H49" s="6" t="s">
         <v>360</v>
       </c>
       <c r="I49" t="s">
@@ -4535,7 +4546,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="50" spans="1:17">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>69</v>
       </c>
@@ -4570,7 +4581,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="51" spans="1:17">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>70</v>
       </c>
@@ -4605,7 +4616,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="52" spans="1:17">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>71</v>
       </c>
@@ -4640,7 +4651,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="53" spans="1:17">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>72</v>
       </c>
@@ -4675,7 +4686,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="54" spans="1:17">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>73</v>
       </c>
@@ -4710,7 +4721,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="55" spans="1:17">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>74</v>
       </c>
@@ -4745,7 +4756,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="56" spans="1:17">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>75</v>
       </c>
@@ -4780,7 +4791,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="57" spans="1:17">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>76</v>
       </c>
@@ -4815,7 +4826,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="58" spans="1:17">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>77</v>
       </c>
@@ -4865,7 +4876,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="59" spans="1:17">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>78</v>
       </c>
@@ -4900,7 +4911,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="60" spans="1:17">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>80</v>
       </c>
@@ -4935,7 +4946,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="61" spans="1:17">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>82</v>
       </c>
@@ -4970,7 +4981,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="62" spans="1:17">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>83</v>
       </c>
@@ -5005,7 +5016,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="63" spans="1:17">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>84</v>
       </c>
@@ -5040,7 +5051,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="64" spans="1:17">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>85</v>
       </c>
@@ -5075,7 +5086,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="65" spans="1:17">
+    <row r="65" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>87</v>
       </c>
@@ -5125,7 +5136,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="66" spans="1:17">
+    <row r="66" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>88</v>
       </c>
@@ -5175,7 +5186,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="67" spans="1:17">
+    <row r="67" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>89</v>
       </c>
@@ -5210,7 +5221,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="68" spans="1:17">
+    <row r="68" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>90</v>
       </c>
@@ -5260,7 +5271,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="69" spans="1:17">
+    <row r="69" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>91</v>
       </c>
@@ -5310,7 +5321,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="70" spans="1:17">
+    <row r="70" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>92</v>
       </c>
@@ -5345,7 +5356,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="71" spans="1:17">
+    <row r="71" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>93</v>
       </c>
@@ -5364,7 +5375,7 @@
       <c r="G71" s="5">
         <v>0.16666666666666666</v>
       </c>
-      <c r="H71" t="s">
+      <c r="H71" s="6" t="s">
         <v>378</v>
       </c>
       <c r="I71" t="s">
@@ -5380,7 +5391,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="72" spans="1:17">
+    <row r="72" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>94</v>
       </c>
@@ -5415,7 +5426,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="73" spans="1:17">
+    <row r="73" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>95</v>
       </c>
@@ -5450,7 +5461,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="74" spans="1:17">
+    <row r="74" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>96</v>
       </c>
@@ -5485,7 +5496,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="75" spans="1:17">
+    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>97</v>
       </c>
@@ -5520,7 +5531,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="76" spans="1:17">
+    <row r="76" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>98</v>
       </c>
@@ -5555,7 +5566,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="77" spans="1:17">
+    <row r="77" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>99</v>
       </c>
@@ -5590,7 +5601,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="78" spans="1:17">
+    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>100</v>
       </c>
@@ -5625,7 +5636,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="79" spans="1:17">
+    <row r="79" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>102</v>
       </c>
@@ -5675,7 +5686,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="80" spans="1:17">
+    <row r="80" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>103</v>
       </c>
@@ -5725,7 +5736,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="81" spans="1:17">
+    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>105</v>
       </c>
@@ -5760,7 +5771,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="82" spans="1:17">
+    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>106</v>
       </c>
@@ -5810,7 +5821,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="83" spans="1:17">
+    <row r="83" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>107</v>
       </c>
@@ -5860,7 +5871,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="84" spans="1:17">
+    <row r="84" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>108</v>
       </c>
@@ -5907,7 +5918,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="85" spans="1:17">
+    <row r="85" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>109</v>
       </c>
@@ -5957,7 +5968,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="86" spans="1:17">
+    <row r="86" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>110</v>
       </c>
@@ -5992,7 +6003,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="87" spans="1:17">
+    <row r="87" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>111</v>
       </c>
@@ -6027,7 +6038,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="88" spans="1:17">
+    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>112</v>
       </c>
@@ -6062,7 +6073,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="89" spans="1:17">
+    <row r="89" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>113</v>
       </c>
@@ -6097,7 +6108,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="90" spans="1:17">
+    <row r="90" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>114</v>
       </c>
@@ -6132,7 +6143,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="91" spans="1:17">
+    <row r="91" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>115</v>
       </c>
@@ -6167,7 +6178,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="92" spans="1:17">
+    <row r="92" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>117</v>
       </c>
@@ -6199,7 +6210,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="93" spans="1:17">
+    <row r="93" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>118</v>
       </c>
@@ -6231,7 +6242,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="94" spans="1:17">
+    <row r="94" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>119</v>
       </c>
@@ -6263,7 +6274,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="95" spans="1:17">
+    <row r="95" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>120</v>
       </c>
@@ -6295,7 +6306,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="96" spans="1:17">
+    <row r="96" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>121</v>
       </c>
@@ -6327,7 +6338,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="97" spans="1:17">
+    <row r="97" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>122</v>
       </c>
@@ -6359,7 +6370,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="98" spans="1:17">
+    <row r="98" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>123</v>
       </c>
@@ -6391,7 +6402,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="99" spans="1:17">
+    <row r="99" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>124</v>
       </c>
@@ -6423,7 +6434,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="100" spans="1:17">
+    <row r="100" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>125</v>
       </c>
@@ -6455,7 +6466,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="101" spans="1:17">
+    <row r="101" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>126</v>
       </c>
@@ -6487,7 +6498,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="102" spans="1:17">
+    <row r="102" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>127</v>
       </c>
@@ -6519,7 +6530,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="103" spans="1:17">
+    <row r="103" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>128</v>
       </c>
@@ -6548,7 +6559,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="104" spans="1:17">
+    <row r="104" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>129</v>
       </c>
@@ -6577,7 +6588,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="105" spans="1:17">
+    <row r="105" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>130</v>
       </c>
@@ -6606,7 +6617,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="106" spans="1:17">
+    <row r="106" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>131</v>
       </c>
@@ -6635,7 +6646,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="107" spans="1:17">
+    <row r="107" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>132</v>
       </c>
@@ -6664,7 +6675,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="108" spans="1:17">
+    <row r="108" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>133</v>
       </c>
@@ -6693,7 +6704,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="109" spans="1:17">
+    <row r="109" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>134</v>
       </c>
@@ -6722,7 +6733,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="110" spans="1:17">
+    <row r="110" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>135</v>
       </c>
@@ -6751,7 +6762,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="111" spans="1:17">
+    <row r="111" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>136</v>
       </c>
@@ -6780,7 +6791,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="112" spans="1:17">
+    <row r="112" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>137</v>
       </c>
@@ -6809,7 +6820,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="113" spans="1:17">
+    <row r="113" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>139</v>
       </c>
@@ -6838,7 +6849,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="114" spans="1:17">
+    <row r="114" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>140</v>
       </c>
@@ -6867,7 +6878,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="115" spans="1:17">
+    <row r="115" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>141</v>
       </c>
@@ -6896,7 +6907,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="116" spans="1:17">
+    <row r="116" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>142</v>
       </c>
@@ -6925,7 +6936,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="117" spans="1:17">
+    <row r="117" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>143</v>
       </c>
@@ -6954,7 +6965,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="118" spans="1:17">
+    <row r="118" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>144</v>
       </c>
@@ -6983,7 +6994,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="119" spans="1:17">
+    <row r="119" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>146</v>
       </c>
@@ -7033,7 +7044,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="120" spans="1:17">
+    <row r="120" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>147</v>
       </c>
@@ -7083,7 +7094,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="121" spans="1:17">
+    <row r="121" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>148</v>
       </c>
@@ -7133,7 +7144,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="122" spans="1:17">
+    <row r="122" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>149</v>
       </c>
@@ -7180,7 +7191,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="123" spans="1:17">
+    <row r="123" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>150</v>
       </c>
@@ -7230,7 +7241,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="124" spans="1:17">
+    <row r="124" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>151</v>
       </c>
@@ -7280,7 +7291,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="125" spans="1:17">
+    <row r="125" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>152</v>
       </c>
@@ -7330,7 +7341,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="126" spans="1:17">
+    <row r="126" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>153</v>
       </c>
@@ -7380,7 +7391,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="127" spans="1:17">
+    <row r="127" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>154</v>
       </c>
@@ -7427,7 +7438,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="128" spans="1:17">
+    <row r="128" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>155</v>
       </c>
@@ -7477,7 +7488,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="129" spans="1:17">
+    <row r="129" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>156</v>
       </c>
@@ -7527,7 +7538,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="130" spans="1:17">
+    <row r="130" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>157</v>
       </c>
@@ -7577,7 +7588,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="131" spans="1:17">
+    <row r="131" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>158</v>
       </c>
@@ -7627,7 +7638,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="132" spans="1:17">
+    <row r="132" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>159</v>
       </c>
@@ -7665,7 +7676,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="133" spans="1:17">
+    <row r="133" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>160</v>
       </c>
@@ -7715,7 +7726,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="134" spans="1:17">
+    <row r="134" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>162</v>
       </c>
@@ -7765,7 +7776,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="135" spans="1:17">
+    <row r="135" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>163</v>
       </c>
@@ -7800,7 +7811,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="136" spans="1:17">
+    <row r="136" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>164</v>
       </c>
@@ -7850,7 +7861,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="137" spans="1:17">
+    <row r="137" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>165</v>
       </c>
@@ -7885,7 +7896,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="138" spans="1:17">
+    <row r="138" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>166</v>
       </c>
@@ -7935,7 +7946,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="139" spans="1:17">
+    <row r="139" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>167</v>
       </c>
@@ -7970,7 +7981,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="140" spans="1:17">
+    <row r="140" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>168</v>
       </c>
@@ -8005,7 +8016,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="141" spans="1:17">
+    <row r="141" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>169</v>
       </c>
@@ -8040,7 +8051,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="142" spans="1:17">
+    <row r="142" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>170</v>
       </c>
@@ -8075,7 +8086,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="143" spans="1:17">
+    <row r="143" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>171</v>
       </c>
@@ -8110,7 +8121,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="144" spans="1:17">
+    <row r="144" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>172</v>
       </c>
@@ -8145,7 +8156,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="145" spans="1:17">
+    <row r="145" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>173</v>
       </c>
@@ -8180,7 +8191,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="146" spans="1:17">
+    <row r="146" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>174</v>
       </c>
@@ -8215,7 +8226,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="147" spans="1:17">
+    <row r="147" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>175</v>
       </c>
@@ -8255,6 +8266,10 @@
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="H49" r:id="rId1" xr:uid="{42A6D4F2-22E6-4A53-941D-F639B8CFB0D6}"/>
+    <hyperlink ref="H71" r:id="rId2" xr:uid="{85A18C07-6E26-4BE3-8C60-D3BC9656E0D6}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>